--- a/docs/Task.xlsx
+++ b/docs/Task.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Kế hoạch chi tiết (UI &amp; API)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Tiến độ thực tế 20-07" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Tiến độ thực tế 21-07" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tiến độ thực tế 22-07" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="d.m"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="18">
     <font>
       <name val="Aptos Narrow"/>
       <color theme="1"/>
@@ -89,8 +90,29 @@
       <color theme="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -109,8 +131,18 @@
         <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border/>
     <border>
       <left style="thin">
@@ -328,11 +360,25 @@
         <color rgb="FFD3D3D3"/>
       </top>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -482,6 +528,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -38395,410 +38462,971 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>BÁO CÁO TIẾN ĐỘ THỰC TẾ — CHỐT NGÀY 21/07/2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Nguồn đối chiếu: lịch sử commit + git status của 2 repo (web-qlsx-start, be-quanlysanxuat); đã chạy pnpm typecheck + eslint (frontend, các file đổi trong ngày) và jest (backend, các module đổi trong ngày) để xác nhận trạng thái, không chỉ dựa vào mô tả code.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Sheet này chỉ BỔ SUNG số liệu ngày 21/07. Các sheet khác giữ nguyên, không sửa, không xoá.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>1. VIỆC ĐÃ LÀM HÔM NAY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Phạm vi</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>Revision sản phẩm (Product Revisions)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Backend + Frontend</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>Frontend xong, đã commit. Backend code xong nhưng CHƯA commit.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>Tab "Lịch sử Revision": danh sách, dialog Tạo/Sửa/Kích hoạt revision, revision switcher trên header — đã nối đúng API thật.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>5 API (list, detail, create, update, activate), tự sinh mã R01/R02..., 6 migration DB (0034-0039) + script backfill revision cho sản phẩm cũ.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>Backend đổi hợp đồng API tạo revision: bắt buộc sourceRevisionId (breaking change so với thiết kế trước) — frontend đã làm đúng theo hợp đồng mới.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>Công đoạn sản xuất (Operations)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Backend + Frontend</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>Backend xong, test xanh, CHƯA commit. Frontend dựng UI xong nhưng CHƯA nối API thật.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>Bảng công đoạn + dialog Thêm/Sửa trong tab "Cấu trúc sản phẩm &amp; Công đoạn".</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>CRUD đầy đủ (vd Cắt laser, Hàn, Sơn tĩnh điện), có seed data, phân biệt INHOUSE/OUTSOURCE.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>Frontend hiện đang chạy bằng DỮ LIỆU GIẢ (mock) — việc còn lại là nối GET/POST/PATCH/DELETE /operations, API đã sẵn sàng phía backend.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>Cấu trúc sản phẩm (cây BOM)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Backend + Frontend</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>Một phần — đúng như cảnh báo trong kế hoạch gốc.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>Bảng cây cấu trúc + dialog thêm/sửa node — đang chạy dữ liệu giả.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Chỉ mới có API ĐỌC (lấy cây BOM theo revision), CHƯA có API tạo/sửa/xoá node.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>Phần khó nhất trong kế hoạch, cần thêm 1-2 ngày backend trước khi frontend nối được thao tác ghi.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>Giao diện Sáng/Tối + hệ màu</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>Xong, đã commit.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>Hệ màu semantic (success/warning/info), nút chuyển Sáng/Tối trên header (next-themes), gộp nhóm sidebar "Danh mục" (Khách hàng, NCC, Sản phẩm, Vật tư).</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Không có thay đổi backend.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>Thuần UI, không phụ thuộc API.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>Menu tài khoản (Profile menu)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Backend + Frontend</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>Frontend xong, đã commit. Backend code xong, CHƯA commit.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>Header hiển thị avatar, email, vai trò thay vì chỉ có tên.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Mở rộng CredentialResDto thêm fullName + avatar.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>Phụ thuộc backend commit + deploy để chạy đúng dữ liệu thật.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>2. KIỂM TRA CHẤT LƯỢNG ĐÃ CHẠY (không chỉ đọc code)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>Việc kiểm tra</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Phạm vi</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>pnpm typecheck</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Frontend, toàn repo</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>Xanh — 0 lỗi.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>pnpm exec eslint</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Frontend — 85 file thay đổi trong 2 commit hôm nay</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>Xanh — 0 lỗi.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>npx jest boms operations product-revisions products users</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Backend — các module thay đổi hôm nay</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>Xanh — 10 bộ test / 131 test. Chưa chạy toàn bộ test suite backend.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>3. VIỆC CÒN THIẾU / RỦI RO</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>a) Toàn bộ phần backend hôm nay (Revisions, Operations, Boms, mở rộng CredentialResDto) mới CODE XONG, CHƯA COMMIT — cần commit sớm để tránh rủi ro mất việc.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>b) Frontend "Công đoạn" và "Cấu trúc sản phẩm" vẫn dùng dữ liệu giả — cần nối API /operations (đã sẵn sàng) và chờ backend bổ sung API ghi cho cây BOM.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>c) API tạo revision đổi sang bắt buộc sourceRevisionId — cần rà lại nếu có nơi khác từng gọi API cũ.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>4. COMMIT TRONG NGÀY</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>Repo</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>Hash</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>Nội dung</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>web-qlsx-start (frontend)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>573c046</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>feat(products): add product revisions and structure management</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>web-qlsx-start (frontend)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>3b49ee5</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>refactor(ui): adopt semantic color tokens and add a dark mode toggle</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>be-quanlysanxuat (backend)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>Không có commit mới trong ngày</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>Thay đổi chỉ nằm ở working tree (git status), chưa commit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" style="45" min="1" max="1"/>
+    <col width="18" customWidth="1" style="45" min="2" max="2"/>
+    <col width="30" customWidth="1" style="45" min="3" max="3"/>
+    <col width="46" customWidth="1" style="45" min="4" max="4"/>
+    <col width="46" customWidth="1" style="45" min="5" max="5"/>
+    <col width="42" customWidth="1" style="45" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="63" t="inlineStr">
+        <is>
+          <t>BÁO CÁO TIẾN ĐỘ THỰC TẾ — CHỐT NGÀY 22/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="64" t="inlineStr">
+        <is>
+          <t>Nguồn đối chiếu: lịch sử commit + git status của 2 repo (web-qlsx-start, be-quanlysanxuat); đã chạy pnpm typecheck + eslint (frontend, các file đổi trong ngày) và jest (backend, các module đổi) để xác nhận trạng thái, không chỉ dựa vào mô tả code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="64" t="inlineStr">
+        <is>
+          <t>Sheet này chỉ BỔ SUNG số liệu ngày 22/07. Các sheet khác giữ nguyên, không sửa, không xoá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>1. VIỆC ĐÃ LÀM HÔM NAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="66" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>Phạm vi</t>
+        </is>
+      </c>
+      <c r="C6" s="67" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="D6" s="67" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E6" s="67" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F6" s="67" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="68" t="inlineStr">
+        <is>
+          <t>Cấu trúc sản phẩm (cây BOM) — CRUD</t>
+        </is>
+      </c>
+      <c r="B7" s="68" t="inlineStr">
+        <is>
+          <t>Backend + Frontend</t>
+        </is>
+      </c>
+      <c r="C7" s="68" t="inlineStr">
+        <is>
+          <t>Cả hai xong, test xanh, CHƯA commit</t>
+        </is>
+      </c>
+      <c r="D7" s="68" t="inlineStr">
+        <is>
+          <t>Thay UI dữ liệu giả bằng CRUD thật: thêm/sửa/xoá hạng mục (dialog + combobox chọn SP WIP/vật tư), cây BOM đọc từ API, dòng gốc "Cấp 0" lấy từ product detail, gate quyền products:bom-manage, thumbnail ảnh ở cột mã bản vẽ.</t>
+        </is>
+      </c>
+      <c r="E7" s="68" t="inlineStr">
+        <is>
+          <t>Bổ sung API GHI cho BOM: POST/PATCH/DELETE /bom/items, DTO create/update, error E050–E055, ràng buộc chỉ sản phẩm WIP mới làm node con.</t>
+        </is>
+      </c>
+      <c r="F7" s="68" t="inlineStr">
+        <is>
+          <t>Bước tiến lớn so với 21-07 (khi đó BOM chỉ có API đọc + frontend mock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="68" t="inlineStr">
+        <is>
+          <t>Đổi giá trị enum ProductType</t>
+        </is>
+      </c>
+      <c r="B8" s="68" t="inlineStr">
+        <is>
+          <t>Backend + Frontend</t>
+        </is>
+      </c>
+      <c r="C8" s="68" t="inlineStr">
+        <is>
+          <t>Xong, CHƯA commit</t>
+        </is>
+      </c>
+      <c r="D8" s="68" t="inlineStr">
+        <is>
+          <t>Thêm enum ProductType (FINISHED_GOOD/WORK_IN_PROGRESS) mirror backend; fix lỗi picker gửi type=WIP (bị backend reject 400) → WORK_IN_PROGRESS.</t>
+        </is>
+      </c>
+      <c r="E8" s="68" t="inlineStr">
+        <is>
+          <t>Migration 0041 đổi tên giá trị enum product type (FG/WIP → FINISHED_GOOD/WORK_IN_PROGRESS).</t>
+        </is>
+      </c>
+      <c r="F8" s="68" t="inlineStr">
+        <is>
+          <t>Breaking change dữ liệu; frontend đã đồng bộ theo enum mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="68" t="inlineStr">
+        <is>
+          <t>Công đoạn theo revision (revision-operations)</t>
+        </is>
+      </c>
+      <c r="B9" s="68" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C9" s="68" t="inlineStr">
+        <is>
+          <t>Backend code xong, test xanh, CHƯA commit; frontend chưa build</t>
+        </is>
+      </c>
+      <c r="D9" s="68" t="inlineStr">
+        <is>
+          <t>Tạm hoãn — chưa nối API.</t>
+        </is>
+      </c>
+      <c r="E9" s="68" t="inlineStr">
+        <is>
+          <t>Module revision-operations mới (hiện READ-ONLY, chỉ GET) + schema + seed.</t>
+        </is>
+      </c>
+      <c r="F9" s="68" t="inlineStr">
+        <is>
+          <t>Chờ backend bổ sung API ghi công đoạn thì frontend mới build tiếp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="68" t="inlineStr">
+        <is>
+          <t>Dọn dẹp cấu trúc cũ (mock)</t>
+        </is>
+      </c>
+      <c r="B10" s="68" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C10" s="68" t="inlineStr">
+        <is>
+          <t>Xong, CHƯA commit</t>
+        </is>
+      </c>
+      <c r="D10" s="68" t="inlineStr">
+        <is>
+          <t>Xoá 11 file UI cấu trúc/công đoạn chạy dữ liệu giả (~1.700 dòng).</t>
+        </is>
+      </c>
+      <c r="E10" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="68" t="inlineStr">
+        <is>
+          <t>Thay bằng BOM thật, giảm dead code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="68" t="inlineStr">
+        <is>
+          <t>Refactor &amp; chất lượng code (FE)</t>
+        </is>
+      </c>
+      <c r="B11" s="68" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C11" s="68" t="inlineStr">
+        <is>
+          <t>Xong, CHƯA commit</t>
+        </is>
+      </c>
+      <c r="D11" s="68" t="inlineStr">
+        <is>
+          <t>Tách useProductBom thành 3 hook con + explicit return type; rename props on{Create,Update,Delete}, activeRevision→currentRevision; helper buildSelectOption; rule CLAUDE.md type/interface linh hoạt.</t>
+        </is>
+      </c>
+      <c r="E11" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="68" t="inlineStr">
+        <is>
+          <t>Nhiều vòng review đặt tên/đồng bộ với người dùng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="68" t="inlineStr">
+        <is>
+          <t>Hạ tầng deploy + màn tải trang (FE)</t>
+        </is>
+      </c>
+      <c r="B12" s="68" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C12" s="68" t="inlineStr">
+        <is>
+          <t>Xong, ĐÃ commit (7 commit)</t>
+        </is>
+      </c>
+      <c r="D12" s="68" t="inlineStr">
+        <is>
+          <t>Cấu hình nixpacks build production; loading screen khi chuyển route; inline CSS chống nháy (FOUC).</t>
+        </is>
+      </c>
+      <c r="E12" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="68" t="inlineStr">
+        <is>
+          <t>Phần DUY NHẤT trong ngày đã commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="65" t="inlineStr">
+        <is>
+          <t>2. KIỂM TRA CHẤT LƯỢNG ĐÃ CHẠY (không chỉ đọc code)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="66" t="inlineStr">
+        <is>
+          <t>Việc kiểm tra</t>
+        </is>
+      </c>
+      <c r="B15" s="67" t="inlineStr">
+        <is>
+          <t>Phạm vi</t>
+        </is>
+      </c>
+      <c r="C15" s="67" t="inlineStr">
+        <is>
+          <t>Kết quả</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="68" t="inlineStr">
+        <is>
+          <t>pnpm typecheck</t>
+        </is>
+      </c>
+      <c r="B16" s="68" t="inlineStr">
+        <is>
+          <t>Frontend, toàn repo</t>
+        </is>
+      </c>
+      <c r="C16" s="68" t="inlineStr">
+        <is>
+          <t>Xanh — 0 lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="68" t="inlineStr">
+        <is>
+          <t>pnpm exec eslint</t>
+        </is>
+      </c>
+      <c r="B17" s="68" t="inlineStr">
+        <is>
+          <t>Frontend — các file BOM + refactor đổi trong ngày</t>
+        </is>
+      </c>
+      <c r="C17" s="68" t="inlineStr">
+        <is>
+          <t>Xanh — 0 lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="68" t="inlineStr">
+        <is>
+          <t>npx jest boms products revision-operations</t>
+        </is>
+      </c>
+      <c r="B18" s="68" t="inlineStr">
+        <is>
+          <t>Backend — các module đổi trong ngày</t>
+        </is>
+      </c>
+      <c r="C18" s="68" t="inlineStr">
+        <is>
+          <t>Xanh — 6 bộ test / 107 test. Chưa chạy toàn bộ suite backend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="65" t="inlineStr">
+        <is>
+          <t>3. VIỆC CÒN THIẾU / RỦI RO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="69" t="inlineStr">
+        <is>
+          <t>a) Gần như TOÀN BỘ việc hôm nay (BOM CRUD frontend+backend, enum ProductType + migration 0041, revision-operations) CHƯA COMMIT ở cả 2 repo — rủi ro mất việc, cần commit sớm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="69" t="inlineStr">
+        <is>
+          <t>b) Migration 0041 đổi giá trị enum product type là breaking change dữ liệu — cần chạy migration + kiểm tra dữ liệu cũ trước khi deploy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="69" t="inlineStr">
+        <is>
+          <t>c) Frontend "Công đoạn" vẫn chưa có (revision-operations chỉ có API đọc) — chờ backend bổ sung API ghi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="69" t="inlineStr">
+        <is>
+          <t>d) activeRevisionId (frontend) chưa đổi theo currentRevision — chưa đồng bộ hoàn toàn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65" t="inlineStr">
+        <is>
+          <t>4. COMMIT TRONG NGÀY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="66" t="inlineStr">
+        <is>
+          <t>Repo</t>
+        </is>
+      </c>
+      <c r="B27" s="67" t="inlineStr">
+        <is>
+          <t>Hash</t>
+        </is>
+      </c>
+      <c r="C27" s="67" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="D27" s="67" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="68" t="inlineStr">
+        <is>
+          <t>web-qlsx-start (frontend)</t>
+        </is>
+      </c>
+      <c r="B28" s="68" t="inlineStr">
+        <is>
+          <t>17e95b5</t>
+        </is>
+      </c>
+      <c r="C28" s="68" t="inlineStr">
+        <is>
+          <t>fix(styles): inline app CSS to prevent flash of unstyled content</t>
+        </is>
+      </c>
+      <c r="D28" s="68" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="68" t="inlineStr">
+        <is>
+          <t>web-qlsx-start (frontend)</t>
+        </is>
+      </c>
+      <c r="B29" s="68" t="inlineStr">
+        <is>
+          <t>d005a98</t>
+        </is>
+      </c>
+      <c r="C29" s="68" t="inlineStr">
+        <is>
+          <t>feat(router): add global loading screen for route transitions</t>
+        </is>
+      </c>
+      <c r="D29" s="68" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="68" t="inlineStr">
+        <is>
+          <t>web-qlsx-start (frontend)</t>
+        </is>
+      </c>
+      <c r="B30" s="68" t="inlineStr">
+        <is>
+          <t>15cdcc0</t>
+        </is>
+      </c>
+      <c r="C30" s="68" t="inlineStr">
+        <is>
+          <t>fix(deploy): pin nixpacks to a nixpkgs archive with nodejs_24</t>
+        </is>
+      </c>
+      <c r="D30" s="68" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="68" t="inlineStr">
+        <is>
+          <t>web-qlsx-start (frontend)</t>
+        </is>
+      </c>
+      <c r="B31" s="68" t="inlineStr">
+        <is>
+          <t>dc77676</t>
+        </is>
+      </c>
+      <c r="C31" s="68" t="inlineStr">
+        <is>
+          <t>fix(deploy): update corepack before preparing pnpm in nixpacks build</t>
+        </is>
+      </c>
+      <c r="D31" s="68" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="68" t="inlineStr">
+        <is>
+          <t>web-qlsx-start (frontend)</t>
+        </is>
+      </c>
+      <c r="B32" s="68" t="inlineStr">
+        <is>
+          <t>7904f1d</t>
+        </is>
+      </c>
+      <c r="C32" s="68" t="inlineStr">
+        <is>
+          <t>fix(deploy): pin nixpacks to nodejs_22, the newest LTS its nixpkgs has</t>
+        </is>
+      </c>
+      <c r="D32" s="68" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="68" t="inlineStr">
+        <is>
+          <t>web-qlsx-start (frontend)</t>
+        </is>
+      </c>
+      <c r="B33" s="68" t="inlineStr">
+        <is>
+          <t>780b8f4</t>
+        </is>
+      </c>
+      <c r="C33" s="68" t="inlineStr">
+        <is>
+          <t>chore(deploy): bump pinned node and pnpm versions to match local dev</t>
+        </is>
+      </c>
+      <c r="D33" s="68" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="68" t="inlineStr">
+        <is>
+          <t>web-qlsx-start (frontend)</t>
+        </is>
+      </c>
+      <c r="B34" s="68" t="inlineStr">
+        <is>
+          <t>c56bb7e</t>
+        </is>
+      </c>
+      <c r="C34" s="68" t="inlineStr">
+        <is>
+          <t>build(deploy): add nixpacks config for the production build</t>
+        </is>
+      </c>
+      <c r="D34" s="68" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="68" t="inlineStr">
+        <is>
+          <t>be-quanlysanxuat (backend)</t>
+        </is>
+      </c>
+      <c r="B35" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="68" t="inlineStr">
+        <is>
+          <t>Không có commit mới trong ngày</t>
+        </is>
+      </c>
+      <c r="D35" s="68" t="inlineStr">
+        <is>
+          <t>Thay đổi (BOM CRUD, enum rename, revision-operations) chỉ nằm ở working tree, chưa commit.</t>
         </is>
       </c>
     </row>
